--- a/dados/excel/municipio_gini.xlsx
+++ b/dados/excel/municipio_gini.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>13829</v>
+        <v>14368</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>0.4391</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
